--- a/school_surveys/009_parent_satisfaction_survey--school_surveys.xlsx
+++ b/school_surveys/009_parent_satisfaction_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>parent_survey_form</t>
+          <t>school_environment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>parent_survey_form</t>
+          <t>School Environment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>school_environment</t>
+          <t>teacher_support</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>school_environment</t>
+          <t>Teacher Support</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>teacher_support</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>teacher_support</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>school_environment</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>school_environment</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>teacher_support</t>
+          <t>school_events</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teacher_support</t>
+          <t>School Events</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,23 +630,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>parent_involvement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Parent Involvement</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,131 +681,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>parent_involvement</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>parent_involvement</t>
+          <t>Suggestions</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>teacher_involvement</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>teacher_involvement</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>parent_support</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>parent_support</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>teacher_support</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>teacher_support</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>overall_satisfaction</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>overall_satisfaction</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -822,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,51 +735,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>teacher_support_choices</t>
+          <t>school_environment_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high',_'value':_'high'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High', 'value': 'high'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>teacher_support_choices</t>
+          <t>school_environment_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium',_'value':_'medium'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium', 'value': 'medium'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>teacher_support_choices</t>
+          <t>school_environment_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'low',_'value':_'low'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Low', 'value': 'low'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -906,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High', 'value': 'high'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -923,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium', 'value': 'medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -940,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low', 'value': 'low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -957,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High', 'value': 'high'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -974,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium', 'value': 'medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -991,12 +876,114 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low', 'value': 'low'}</t>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>school_events_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>school_events_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>school_events_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>parent_involvement_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>parent_involvement_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>parent_involvement_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
